--- a/data/trans_bre/IP2004-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP2004-Clase-trans_bre.xlsx
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,5; 8,56</t>
+          <t>1,53; 9,19</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 6,38</t>
+          <t>-0,62; 7,53</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 6,05</t>
+          <t>-1,57; 5,49</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,78; 0,71</t>
+          <t>-4,6; 0,66</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -760,22 +760,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,04; 8,36</t>
+          <t>-0,06; 8,32</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 5,54</t>
+          <t>-0,61; 5,46</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,63; 5,98</t>
+          <t>0,64; 6,83</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-6,27; 0,0</t>
+          <t>-6,41; 0,0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,6; -0,68</t>
+          <t>-6,23; -0,68</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,37; 4,17</t>
+          <t>-3,7; 4,11</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,5</t>
+          <t>0,0; 7,42</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 6,07</t>
+          <t>-1,75; 5,94</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,64; 0,79</t>
+          <t>-4,84; 0,7</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 2,48</t>
+          <t>-2,36; 2,58</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 5,28</t>
+          <t>-0,45; 4,87</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,16; 0,88</t>
+          <t>-3,58; 0,82</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-81,92; 50,44</t>
+          <t>-83,25; 46,63</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-75,8; 273,07</t>
+          <t>-77,92; 262,83</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-27,34; 771,07</t>
+          <t>-24,15; 770,97</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 240,6</t>
+          <t>-100,0; 214,74</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,32; 2,79</t>
+          <t>-6,47; 2,48</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,22; 3,68</t>
+          <t>-5,37; 3,8</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,91; 2,68</t>
+          <t>-4,9; 2,51</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,63; 2,83</t>
+          <t>-3,77; 3,04</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-82,29; 86,35</t>
+          <t>-80,86; 86,97</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-67,29; 146,1</t>
+          <t>-68,32; 155,54</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-78,02; 133,65</t>
+          <t>-82,08; 139,08</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-87,86; 378,47</t>
+          <t>-86,83; 371,28</t>
         </is>
       </c>
     </row>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-2,51; 5,77</t>
+          <t>-3,44; 5,55</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 8,04</t>
+          <t>-0,96; 9,09</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 4,27</t>
+          <t>-2,16; 3,39</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-6,79; 4,67</t>
+          <t>-7,05; 4,8</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 1,48</t>
+          <t>-1,57; 1,5</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 2,11</t>
+          <t>-0,76; 2,2</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 2,65</t>
+          <t>-0,21; 2,58</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 0,12</t>
+          <t>-2,3; 0,09</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-42,39; 71,72</t>
+          <t>-44,4; 74,1</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-28,34; 136,19</t>
+          <t>-28,14; 134,03</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-6,88; 256,83</t>
+          <t>-16,68; 252,85</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-77,82; 15,97</t>
+          <t>-77,53; 12,8</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP2004-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP2004-Clase-trans_bre.xlsx
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,53; 9,19</t>
+          <t>1,53; 8,87</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 7,53</t>
+          <t>-0,59; 6,61</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 5,49</t>
+          <t>-1,59; 4,95</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,6; 0,66</t>
+          <t>-4,4; 0,41</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -760,22 +760,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 8,32</t>
+          <t>-0,05; 8,08</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 5,46</t>
+          <t>-0,6; 6,12</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,64; 6,83</t>
+          <t>0,64; 6,75</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-6,41; 0,0</t>
+          <t>-6,2; 0,0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,23; -0,68</t>
+          <t>-5,85; -0,68</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,7; 4,11</t>
+          <t>-3,43; 4,17</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,42</t>
+          <t>0,0; 7,85</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 5,94</t>
+          <t>-1,76; 6,33</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,84; 0,7</t>
+          <t>-5,09; 0,6</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 2,58</t>
+          <t>-2,56; 2,61</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 4,87</t>
+          <t>-0,63; 4,84</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,58; 0,82</t>
+          <t>-3,44; 0,66</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-83,25; 46,63</t>
+          <t>-85,82; 45,21</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-77,92; 262,83</t>
+          <t>-73,43; 277,28</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-24,15; 770,97</t>
+          <t>-39,47; 530,52</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 214,74</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,47; 2,48</t>
+          <t>-6,06; 2,46</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,37; 3,8</t>
+          <t>-5,31; 3,79</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,9; 2,51</t>
+          <t>-4,96; 2,54</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,77; 3,04</t>
+          <t>-3,76; 2,94</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-80,86; 86,97</t>
+          <t>-78,37; 92,03</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-68,32; 155,54</t>
+          <t>-66,95; 154,49</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-82,08; 139,08</t>
+          <t>-80,38; 129,69</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-86,83; 371,28</t>
+          <t>-88,51; 465,83</t>
         </is>
       </c>
     </row>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-3,44; 5,55</t>
+          <t>-3,1; 5,3</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 9,09</t>
+          <t>-0,87; 8,28</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 3,39</t>
+          <t>-2,17; 3,37</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-7,05; 4,8</t>
+          <t>-6,27; 4,62</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 1,5</t>
+          <t>-1,55; 1,4</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 2,2</t>
+          <t>-0,95; 2,17</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 2,58</t>
+          <t>-0,2; 2,55</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 0,09</t>
+          <t>-2,25; 0,31</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-44,4; 74,1</t>
+          <t>-42,08; 68,15</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-28,14; 134,03</t>
+          <t>-34,39; 129,75</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-16,68; 252,85</t>
+          <t>-15,06; 220,83</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-77,53; 12,8</t>
+          <t>-75,89; 28,05</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP2004-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP2004-Clase-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-1,78</t>
+          <t>-1,63</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-72,65%</t>
+          <t>-68,24%</t>
         </is>
       </c>
     </row>
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,53; 8,87</t>
+          <t>1,5; 8,56</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 6,61</t>
+          <t>-0,63; 6,38</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 4,95</t>
+          <t>-1,58; 6,05</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,4; 0,41</t>
+          <t>-4,53; 0,97</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-1,73</t>
+          <t>-1,66</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -760,22 +760,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,05; 8,08</t>
+          <t>-0,04; 8,36</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 6,12</t>
+          <t>-0,67; 5,54</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,64; 6,75</t>
+          <t>0,63; 5,98</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-6,2; 0,0</t>
+          <t>-6,34; 0,0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,64</t>
+          <t>0,8</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>73,9%</t>
+          <t>98,98%</t>
         </is>
       </c>
     </row>
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,85; -0,68</t>
+          <t>-5,6; -0,68</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 4,17</t>
+          <t>-3,37; 4,17</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,85</t>
+          <t>0,0; 7,5</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 6,33</t>
+          <t>-1,65; 6,57</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-0,99</t>
+          <t>-0,94</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-51,14%</t>
+          <t>-43,79%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-5,09; 0,6</t>
+          <t>-4,64; 0,79</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 2,61</t>
+          <t>-2,49; 2,48</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 4,84</t>
+          <t>-0,52; 5,28</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,44; 0,66</t>
+          <t>-3,32; 1,26</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-85,82; 45,21</t>
+          <t>-81,92; 50,44</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-73,43; 277,28</t>
+          <t>-75,8; 273,07</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-39,47; 530,52</t>
+          <t>-27,34; 771,07</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 296,45</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-0,5</t>
+          <t>-0,53</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-18,47%</t>
+          <t>-18,97%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,06; 2,46</t>
+          <t>-6,32; 2,79</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,31; 3,79</t>
+          <t>-5,22; 3,68</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,96; 2,54</t>
+          <t>-4,91; 2,68</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,76; 2,94</t>
+          <t>-3,87; 2,86</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-78,37; 92,03</t>
+          <t>-82,29; 86,35</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-66,95; 154,49</t>
+          <t>-67,29; 146,1</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-80,38; 129,69</t>
+          <t>-78,02; 133,65</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-88,51; 465,83</t>
+          <t>-89,41; 381,44</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-0,77</t>
+          <t>-0,03</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-24,7%</t>
+          <t>-1,09%</t>
         </is>
       </c>
     </row>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-3,1; 5,3</t>
+          <t>-2,51; 5,77</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 8,28</t>
+          <t>-0,9; 8,04</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 3,37</t>
+          <t>-2,14; 4,27</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-6,27; 4,62</t>
+          <t>-4,46; 5,77</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-1,01</t>
+          <t>-0,87</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-46,06%</t>
+          <t>-40,06%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 1,4</t>
+          <t>-1,51; 1,48</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 2,17</t>
+          <t>-0,82; 2,11</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 2,55</t>
+          <t>-0,1; 2,65</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 0,31</t>
+          <t>-2,25; 0,32</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-42,08; 68,15</t>
+          <t>-42,39; 71,72</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-34,39; 129,75</t>
+          <t>-28,34; 136,19</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-15,06; 220,83</t>
+          <t>-6,88; 256,83</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-75,89; 28,05</t>
+          <t>-75,98; 29,75</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP2004-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP2004-Clase-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,171 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>3,94</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>2,02</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,63</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-1,63</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>267,28%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>79,87%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-68,24%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>3.935693306477857</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>2.021076561591764</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.6318593978270221</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-1.626831014036214</v>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>2.672756311651599</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>0.7986765327105839</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>-0.6824019067303915</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>1,5; 8,56</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-0,63; 6,38</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-1,58; 6,05</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-4,53; 0,97</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>1.500989010594758</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-0.6287272701777267</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-1.583224356191822</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-4.533186501547998</v>
+      </c>
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr"/>
+      <c r="I5" s="6" t="inlineStr"/>
+      <c r="J5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>8.563276811073575</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>6.37557315340883</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>6.04967682663572</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>0.9737149506004337</v>
+      </c>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr"/>
+      <c r="I6" s="6" t="inlineStr"/>
+      <c r="J6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Grupo III</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>3,09</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>1,67</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>2,32</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-1,66</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>389,03%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>243,53%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-0,04; 8,36</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-0,67; 5,54</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>0,63; 5,98</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-6,34; 0,0</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>3.093179620477956</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>1.667321484632964</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>2.319049738866662</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-1.657578760153276</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>3.89025754070256</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>2.435341095301951</v>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Grupo IV y V</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-2,1</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>0,5</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>2,13</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,8</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>26,46%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>98,98%</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-0.03526651968734874</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-0.6680047480223104</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.6343993101365271</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-6.335608782606567</v>
+      </c>
+      <c r="G8" s="6" t="inlineStr"/>
+      <c r="H8" s="6" t="inlineStr"/>
+      <c r="I8" s="6" t="inlineStr"/>
+      <c r="J8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-5,6; -0,68</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-3,37; 4,17</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 7,5</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-1,65; 6,57</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>8.36335653922063</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>5.540213603808297</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>5.984495208322556</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="6" t="inlineStr"/>
+      <c r="H9" s="6" t="inlineStr"/>
+      <c r="I9" s="6" t="inlineStr"/>
+      <c r="J9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Grupo VI</t>
+          <t>Grupo IV y V</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,299 +791,185 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-1,96</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>0,05</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>2,04</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-0,94</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-49,86%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2,5%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>109,85%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-43,79%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-2.099656392585684</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.4975679414973355</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>2.125871623416533</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>0.7981766251108845</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>0.2646311666542587</v>
+      </c>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>0.989754650398444</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-4,64; 0,79</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-2,49; 2,48</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-0,52; 5,28</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-3,32; 1,26</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-81,92; 50,44</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-75,8; 273,07</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-27,34; 771,07</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 296,45</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-5.602609073159289</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-3.365340682254643</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-1.648481359382218</v>
+      </c>
+      <c r="G11" s="6" t="inlineStr"/>
+      <c r="H11" s="6" t="inlineStr"/>
+      <c r="I11" s="6" t="inlineStr"/>
+      <c r="J11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Grupo VII</t>
-        </is>
-      </c>
+      <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>-0.6808435407714017</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>4.170778173656282</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>7.496293645066898</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>6.569626435098737</v>
+      </c>
+      <c r="G12" s="6" t="inlineStr"/>
+      <c r="H12" s="6" t="inlineStr"/>
+      <c r="I12" s="6" t="inlineStr"/>
+      <c r="J12" s="6" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>-1,9</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-0,72</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-1,08</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-0,53</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-32,82%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-13,38%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>-26,28%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>-18,97%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-6,32; 2,79</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-5,22; 3,68</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-4,91; 2,68</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-3,87; 2,86</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-82,29; 86,35</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-67,29; 146,1</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-78,02; 133,65</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-89,41; 381,44</t>
-        </is>
+      <c r="C13" s="5" t="n">
+        <v>-1.963369428171472</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.05443154430033077</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>2.043419427377605</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-0.9396524962824673</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.4986219559662518</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0.02497691994099572</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>1.098525870722406</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>-0.4379456041424338</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>No ha trabajado</t>
-        </is>
-      </c>
+      <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>1,36</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>2,12</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>0,03</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-0,03</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>67,87%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>239,29%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>2,55%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>-1,09%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-4.639452040475916</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-2.494243900141257</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-0.517886730596849</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-3.323833578692016</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.8192094478202676</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.7580308373875428</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.2733654910802985</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>-2,51; 5,77</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>-0,9; 8,04</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>-2,14; 4,27</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>-4,46; 5,77</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.7917193371407523</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>2.48323774224306</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>5.275233948666673</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>1.262117087825474</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.5044144093516399</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>2.730731200272744</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>7.710681196121189</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>2.96450143277786</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Grupo VII</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1210,97 +977,281 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>-0,03</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>0,68</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>1,15</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-0,87</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-1,18%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>30,22%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>71,58%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>-40,06%</t>
-        </is>
+      <c r="C16" s="5" t="n">
+        <v>-1.897112066978036</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-0.717890328039783</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-1.082897060402516</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>-0.5292846342858152</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>-0.3281839826745191</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>-0.1337766065016536</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>-0.2627683816858358</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>-0.1897201704184892</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>-1,51; 1,48</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>-0,82; 2,11</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>-0,1; 2,65</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>-2,25; 0,32</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>-42,39; 71,72</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>-28,34; 136,19</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>-6,88; 256,83</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>-75,98; 29,75</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-6.315521237739652</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-5.220669939178655</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-4.914561999713336</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-3.867952495147541</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.8229155586161401</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.6728804346437497</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.78019191116951</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-0.8941011506587671</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>2.786373684042753</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>3.67653200899804</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>2.678860014885247</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>2.855978302858533</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0.8635211004722294</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>1.460954073878918</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>1.336467678163941</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>3.814397522932426</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>1.364342395203481</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>2.115345626010475</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>0.02708490483209446</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>-0.02508546527159455</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>0.678673310033261</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>2.392883505166157</v>
+      </c>
+      <c r="I19" s="6" t="n">
+        <v>0.02551165335569028</v>
+      </c>
+      <c r="J19" s="6" t="n">
+        <v>-0.0109411126648991</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>-2.508408078314683</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>-0.9015255315670618</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>-2.136763043412144</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>-4.463012034542682</v>
+      </c>
+      <c r="G20" s="6" t="inlineStr"/>
+      <c r="H20" s="6" t="inlineStr"/>
+      <c r="I20" s="6" t="inlineStr"/>
+      <c r="J20" s="6" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>5.769552159581219</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>8.041716849264205</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>4.267121281827494</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>5.768003314124172</v>
+      </c>
+      <c r="G21" s="6" t="inlineStr"/>
+      <c r="H21" s="6" t="inlineStr"/>
+      <c r="I21" s="6" t="inlineStr"/>
+      <c r="J21" s="6" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>-0.03362689870392982</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>0.6805770208834115</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>1.148858415719513</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>-0.8674281104956943</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>-0.01180455889063161</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>0.3022117373797311</v>
+      </c>
+      <c r="I22" s="6" t="n">
+        <v>0.7157950357635822</v>
+      </c>
+      <c r="J22" s="6" t="n">
+        <v>-0.4005572701170254</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>-1.507604775606343</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-0.8207383105328586</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-0.1007040259837449</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>-2.245141161900484</v>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>-0.4239097596036347</v>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>-0.2833834894769762</v>
+      </c>
+      <c r="I23" s="6" t="n">
+        <v>-0.06879219062923091</v>
+      </c>
+      <c r="J23" s="6" t="n">
+        <v>-0.7598348423880547</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>1.479902093622804</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>2.113476593296288</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>2.646917181636304</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>0.3219116485939824</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>0.7172311448209571</v>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>1.361865115651989</v>
+      </c>
+      <c r="I24" s="6" t="n">
+        <v>2.568285103851725</v>
+      </c>
+      <c r="J24" s="6" t="n">
+        <v>0.297477586890902</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1308,16 +1259,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="C1:F1"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
